--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -10,12 +10,19 @@
     <sheet name="Include from TRE_R21-Fonction" r:id="rId4" sheetId="2"/>
     <sheet name="Include from TRE_R96-AutreFon" r:id="rId5" sheetId="3"/>
     <sheet name="Include from TRE_R85-RolePris" r:id="rId6" sheetId="4"/>
+    <sheet name="Include from TRE_R22-GenreAct" r:id="rId7" sheetId="5"/>
+    <sheet name="Include from TRE_R23-ModeExer" r:id="rId8" sheetId="6"/>
+    <sheet name="Include from TRE_R24-TypeActi" r:id="rId9" sheetId="7"/>
+    <sheet name="Include from TRE_R32-StatutHo" r:id="rId10" sheetId="8"/>
+    <sheet name="Include from TRE_R24-TypeActi 2" r:id="rId11" sheetId="9"/>
+    <sheet name="Include from TRE_G05-SousSect" r:id="rId12" sheetId="10"/>
+    <sheet name="Include from TRE_R06-SectionT" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
   <si>
     <t>Property</t>
   </si>
@@ -32,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -50,7 +57,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -62,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,6 +127,24 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R85-RolePriseCharge/FHIR/TRE-R85-RolePriseCharge</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R22-GenreActivite/FHIR/TRE-R22-GenreActivite</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R23-ModeExercice/FHIR/TRE-R23-ModeExercice</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R24-TypeActiviteLiberale/FHIR/TRE-R24-TypeActiviteLiberale</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R32-StatutHospitalier/FHIR/TRE-R32-StatutHospitalier</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_G05-SousSectionTableauCNOP/FHIR/TRE-G05-SousSectionTableauCNOP</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R06-SectionTableauCNOP/FHIR/TRE-R06-SectionTableauCNOP</t>
   </si>
 </sst>
 </file>
@@ -389,6 +414,86 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B4"/>
@@ -507,4 +612,204 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -7,16 +7,16 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R21-Fonction" r:id="rId4" sheetId="2"/>
-    <sheet name="Include from TRE_R96-AutreFon" r:id="rId5" sheetId="3"/>
-    <sheet name="Include from TRE_R85-RolePris" r:id="rId6" sheetId="4"/>
-    <sheet name="Include from TRE_R22-GenreAct" r:id="rId7" sheetId="5"/>
-    <sheet name="Include from TRE_R23-ModeExer" r:id="rId8" sheetId="6"/>
-    <sheet name="Include from TRE_R24-TypeActi" r:id="rId9" sheetId="7"/>
-    <sheet name="Include from TRE_R32-StatutHo" r:id="rId10" sheetId="8"/>
-    <sheet name="Include from TRE_R24-TypeActi 2" r:id="rId11" sheetId="9"/>
-    <sheet name="Include from TRE_G05-SousSect" r:id="rId12" sheetId="10"/>
-    <sheet name="Include from TRE_R06-SectionT" r:id="rId13" sheetId="11"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
+    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
+    <sheet name="Include #3" r:id="rId7" sheetId="5"/>
+    <sheet name="Include #4" r:id="rId8" sheetId="6"/>
+    <sheet name="Include #5" r:id="rId9" sheetId="7"/>
+    <sheet name="Include #6" r:id="rId10" sheetId="8"/>
+    <sheet name="Include #7" r:id="rId11" sheetId="9"/>
+    <sheet name="Include #8" r:id="rId12" sheetId="10"/>
+    <sheet name="Include #9" r:id="rId13" sheetId="11"/>
   </sheets>
 </workbook>
 </file>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -39,7 +39,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
+++ b/main/ig/ValueSet-fr-core-vs-practitioner-role-exercice.xlsx
@@ -69,7 +69,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
